--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/pre LAM_HRM-2031-0480/Panel 02/front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Front_Summary.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J40"/>
+  <dimension ref="A1:J80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.35217</v>
+        <v>17.32505</v>
       </c>
       <c r="D2" t="n">
-        <v>17.20343</v>
+        <v>16.9677</v>
       </c>
       <c r="E2" t="n">
-        <v>17.81329</v>
+        <v>17.15767</v>
       </c>
       <c r="F2" t="n">
-        <v>44.74748</v>
+        <v>44.20602</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05181</v>
+        <v>0.05184</v>
       </c>
       <c r="H2" t="n">
-        <v>1.88188</v>
+        <v>1.90029</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.05212</v>
+        <v>17.42583</v>
       </c>
       <c r="D3" t="n">
-        <v>17.21747</v>
+        <v>16.6381</v>
       </c>
       <c r="E3" t="n">
-        <v>17.23363</v>
+        <v>17.03912</v>
       </c>
       <c r="F3" t="n">
-        <v>44.42153</v>
+        <v>43.52895</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0516</v>
+        <v>0.05213</v>
       </c>
       <c r="H3" t="n">
-        <v>1.87849</v>
+        <v>1.87593</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.13159</v>
+        <v>17.43596</v>
       </c>
       <c r="D4" t="n">
-        <v>17.12488</v>
+        <v>17.15152</v>
       </c>
       <c r="E4" t="n">
-        <v>16.92714</v>
+        <v>17.24844</v>
       </c>
       <c r="F4" t="n">
-        <v>43.52325</v>
+        <v>43.87119</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05137</v>
+        <v>0.05176</v>
       </c>
       <c r="H4" t="n">
-        <v>1.87852</v>
+        <v>1.85697</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>16.8923</v>
+        <v>17.32792</v>
       </c>
       <c r="D5" t="n">
-        <v>17.24988</v>
+        <v>17.03111</v>
       </c>
       <c r="E5" t="n">
-        <v>16.96484</v>
+        <v>17.17067</v>
       </c>
       <c r="F5" t="n">
-        <v>44.14733</v>
+        <v>43.70854</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05244</v>
+        <v>0.05236</v>
       </c>
       <c r="H5" t="n">
-        <v>1.87742</v>
+        <v>1.85058</v>
       </c>
     </row>
     <row r="6">
@@ -560,22 +560,22 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>16.82628</v>
+        <v>17.28547</v>
       </c>
       <c r="D6" t="n">
-        <v>17.05504</v>
+        <v>17.1575</v>
       </c>
       <c r="E6" t="n">
-        <v>17.42708</v>
+        <v>17.25195</v>
       </c>
       <c r="F6" t="n">
-        <v>44.07845</v>
+        <v>44.48098</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05265</v>
+        <v>0.05161</v>
       </c>
       <c r="H6" t="n">
-        <v>1.85731</v>
+        <v>1.86342</v>
       </c>
     </row>
     <row r="7">
@@ -585,22 +585,22 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.15936</v>
+        <v>17.2814</v>
       </c>
       <c r="D7" t="n">
-        <v>17.27427</v>
+        <v>16.81677</v>
       </c>
       <c r="E7" t="n">
-        <v>16.86487</v>
+        <v>17.05425</v>
       </c>
       <c r="F7" t="n">
-        <v>44.22588</v>
+        <v>44.31643</v>
       </c>
       <c r="G7" t="n">
-        <v>0.05281</v>
+        <v>0.05214</v>
       </c>
       <c r="H7" t="n">
-        <v>1.85977</v>
+        <v>1.88273</v>
       </c>
     </row>
     <row r="8">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>16.74725</v>
+        <v>17.53732</v>
       </c>
       <c r="D8" t="n">
-        <v>16.7905</v>
+        <v>17.07308</v>
       </c>
       <c r="E8" t="n">
-        <v>17.26008</v>
+        <v>17.08206</v>
       </c>
       <c r="F8" t="n">
-        <v>43.36324</v>
+        <v>43.90345</v>
       </c>
       <c r="G8" t="n">
-        <v>0.05345</v>
+        <v>0.0508</v>
       </c>
       <c r="H8" t="n">
-        <v>1.89032</v>
+        <v>1.893</v>
       </c>
     </row>
     <row r="9">
@@ -635,22 +635,22 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>17.25376</v>
+        <v>17.54627</v>
       </c>
       <c r="D9" t="n">
-        <v>17.19989</v>
+        <v>17.20386</v>
       </c>
       <c r="E9" t="n">
-        <v>17.0037</v>
+        <v>17.29174</v>
       </c>
       <c r="F9" t="n">
-        <v>43.61247</v>
+        <v>43.29943</v>
       </c>
       <c r="G9" t="n">
-        <v>0.05118</v>
+        <v>0.05158</v>
       </c>
       <c r="H9" t="n">
-        <v>1.8544</v>
+        <v>1.84174</v>
       </c>
     </row>
     <row r="10">
@@ -660,22 +660,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>17.44777</v>
+        <v>17.35206</v>
       </c>
       <c r="D10" t="n">
-        <v>17.21842</v>
+        <v>17.24779</v>
       </c>
       <c r="E10" t="n">
-        <v>17.26709</v>
+        <v>17.28417</v>
       </c>
       <c r="F10" t="n">
-        <v>43.56488</v>
+        <v>42.5602</v>
       </c>
       <c r="G10" t="n">
-        <v>0.05273</v>
+        <v>0.05126</v>
       </c>
       <c r="H10" t="n">
-        <v>1.91375</v>
+        <v>1.8791</v>
       </c>
     </row>
     <row r="11">
@@ -718,26 +718,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pad 1</t>
+          <t>Pad 2</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>17.96072</v>
+        <v>17.74178</v>
       </c>
       <c r="D12" t="n">
-        <v>16.94273</v>
+        <v>17.01227</v>
       </c>
       <c r="E12" t="n">
-        <v>17.16806</v>
+        <v>17.14533</v>
       </c>
       <c r="F12" t="n">
-        <v>43.71492</v>
+        <v>44.11341</v>
       </c>
       <c r="G12" t="n">
-        <v>0.05124</v>
+        <v>0.05319</v>
       </c>
       <c r="H12" t="n">
-        <v>1.88324</v>
+        <v>1.885</v>
       </c>
     </row>
     <row r="13">
@@ -747,22 +747,22 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>17.57285</v>
+        <v>17.26963</v>
       </c>
       <c r="D13" t="n">
-        <v>17.16601</v>
+        <v>16.89513</v>
       </c>
       <c r="E13" t="n">
-        <v>17.23884</v>
+        <v>17.02305</v>
       </c>
       <c r="F13" t="n">
-        <v>43.62092</v>
+        <v>44.28816</v>
       </c>
       <c r="G13" t="n">
-        <v>0.05311</v>
+        <v>0.05247</v>
       </c>
       <c r="H13" t="n">
-        <v>1.8707</v>
+        <v>1.86627</v>
       </c>
     </row>
     <row r="14">
@@ -772,22 +772,22 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>17.24045</v>
+        <v>17.36633</v>
       </c>
       <c r="D14" t="n">
-        <v>16.50182</v>
+        <v>16.81143</v>
       </c>
       <c r="E14" t="n">
-        <v>17.1654</v>
+        <v>17.26893</v>
       </c>
       <c r="F14" t="n">
-        <v>43.57164</v>
+        <v>43.98053</v>
       </c>
       <c r="G14" t="n">
-        <v>0.05147</v>
+        <v>0.05179</v>
       </c>
       <c r="H14" t="n">
-        <v>1.86583</v>
+        <v>1.88812</v>
       </c>
     </row>
     <row r="15">
@@ -797,22 +797,22 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>17.10944</v>
+        <v>17.35453</v>
       </c>
       <c r="D15" t="n">
-        <v>17.19126</v>
+        <v>17.11643</v>
       </c>
       <c r="E15" t="n">
-        <v>16.8935</v>
+        <v>17.19111</v>
       </c>
       <c r="F15" t="n">
-        <v>43.85705</v>
+        <v>44.661</v>
       </c>
       <c r="G15" t="n">
-        <v>0.05236</v>
+        <v>0.05409</v>
       </c>
       <c r="H15" t="n">
-        <v>1.85131</v>
+        <v>1.86652</v>
       </c>
     </row>
     <row r="16">
@@ -822,22 +822,22 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>17.06755</v>
+        <v>17.35632</v>
       </c>
       <c r="D16" t="n">
-        <v>17.17347</v>
+        <v>16.96717</v>
       </c>
       <c r="E16" t="n">
-        <v>17.31486</v>
+        <v>17.16593</v>
       </c>
       <c r="F16" t="n">
-        <v>44.15555</v>
+        <v>43.81115</v>
       </c>
       <c r="G16" t="n">
-        <v>0.05171</v>
+        <v>0.05218</v>
       </c>
       <c r="H16" t="n">
-        <v>1.86115</v>
+        <v>1.84955</v>
       </c>
     </row>
     <row r="17">
@@ -847,22 +847,22 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>17.12963</v>
+        <v>17.40291</v>
       </c>
       <c r="D17" t="n">
-        <v>17.23542</v>
+        <v>17.07813</v>
       </c>
       <c r="E17" t="n">
-        <v>17.48559</v>
+        <v>17.21097</v>
       </c>
       <c r="F17" t="n">
-        <v>44.1745</v>
+        <v>43.54911</v>
       </c>
       <c r="G17" t="n">
-        <v>0.05255</v>
+        <v>0.05154</v>
       </c>
       <c r="H17" t="n">
-        <v>1.86884</v>
+        <v>1.89678</v>
       </c>
     </row>
     <row r="18">
@@ -872,22 +872,22 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>17.44194</v>
+        <v>17.1282</v>
       </c>
       <c r="D18" t="n">
-        <v>17.26389</v>
+        <v>16.85103</v>
       </c>
       <c r="E18" t="n">
-        <v>17.49116</v>
+        <v>16.94375</v>
       </c>
       <c r="F18" t="n">
-        <v>44.21338</v>
+        <v>43.61251</v>
       </c>
       <c r="G18" t="n">
-        <v>0.05219</v>
+        <v>0.05186</v>
       </c>
       <c r="H18" t="n">
-        <v>1.85116</v>
+        <v>1.854</v>
       </c>
     </row>
     <row r="19">
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>16.99805</v>
+        <v>17.54472</v>
       </c>
       <c r="D19" t="n">
-        <v>16.90468</v>
+        <v>16.8322</v>
       </c>
       <c r="E19" t="n">
-        <v>16.96928</v>
+        <v>17.3344</v>
       </c>
       <c r="F19" t="n">
-        <v>44.19176</v>
+        <v>44.62771</v>
       </c>
       <c r="G19" t="n">
-        <v>0.05308</v>
+        <v>0.05267</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8471</v>
+        <v>1.84969</v>
       </c>
     </row>
     <row r="20">
@@ -922,33 +922,43 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>16.86874</v>
+        <v>17.18404</v>
       </c>
       <c r="D20" t="n">
-        <v>17.05482</v>
+        <v>17.03976</v>
       </c>
       <c r="E20" t="n">
-        <v>16.99223</v>
+        <v>17.15305</v>
       </c>
       <c r="F20" t="n">
-        <v>43.77312</v>
+        <v>44.59766</v>
       </c>
       <c r="G20" t="n">
-        <v>0.0516</v>
+        <v>0.05141</v>
       </c>
       <c r="H20" t="n">
-        <v>1.86048</v>
+        <v>1.88446</v>
       </c>
     </row>
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>Dimple</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bump</t>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Radius</t>
         </is>
       </c>
     </row>
@@ -960,14 +970,20 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>via 1</t>
+          <t>SR Pad 1</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.61084</v>
+        <v>16.37955</v>
       </c>
       <c r="D22" t="n">
-        <v>1.14803</v>
+        <v>16.09898</v>
+      </c>
+      <c r="E22" t="n">
+        <v>16.24152</v>
+      </c>
+      <c r="F22" t="n">
+        <v>257.13503</v>
       </c>
     </row>
     <row r="23">
@@ -977,10 +993,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.62898</v>
+        <v>16.12061</v>
       </c>
       <c r="D23" t="n">
-        <v>1.14016</v>
+        <v>16.00091</v>
+      </c>
+      <c r="E23" t="n">
+        <v>16.06554</v>
+      </c>
+      <c r="F23" t="n">
+        <v>264.79436</v>
       </c>
     </row>
     <row r="24">
@@ -990,10 +1012,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.6241</v>
+        <v>16.46264</v>
       </c>
       <c r="D24" t="n">
-        <v>1.14064</v>
+        <v>16.09919</v>
+      </c>
+      <c r="E24" t="n">
+        <v>16.18594</v>
+      </c>
+      <c r="F24" t="n">
+        <v>262.96791</v>
       </c>
     </row>
     <row r="25">
@@ -1003,10 +1031,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.63003</v>
+        <v>16.45596</v>
       </c>
       <c r="D25" t="n">
-        <v>1.14823</v>
+        <v>15.90945</v>
+      </c>
+      <c r="E25" t="n">
+        <v>16.31135</v>
+      </c>
+      <c r="F25" t="n">
+        <v>266.15412</v>
       </c>
     </row>
     <row r="26">
@@ -1016,10 +1050,16 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.62581</v>
+        <v>16.09601</v>
       </c>
       <c r="D26" t="n">
-        <v>1.13225</v>
+        <v>15.81774</v>
+      </c>
+      <c r="E26" t="n">
+        <v>16.04529</v>
+      </c>
+      <c r="F26" t="n">
+        <v>260.09029</v>
       </c>
     </row>
     <row r="27">
@@ -1029,10 +1069,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.62837</v>
+        <v>16.16178</v>
       </c>
       <c r="D27" t="n">
-        <v>1.14781</v>
+        <v>16.10037</v>
+      </c>
+      <c r="E27" t="n">
+        <v>16.10301</v>
+      </c>
+      <c r="F27" t="n">
+        <v>256.93979</v>
       </c>
     </row>
     <row r="28">
@@ -1042,10 +1088,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.63785</v>
+        <v>16.35416</v>
       </c>
       <c r="D28" t="n">
-        <v>1.14749</v>
+        <v>15.87304</v>
+      </c>
+      <c r="E28" t="n">
+        <v>16.27155</v>
+      </c>
+      <c r="F28" t="n">
+        <v>254.77149</v>
       </c>
     </row>
     <row r="29">
@@ -1055,10 +1107,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.62746</v>
+        <v>16.28482</v>
       </c>
       <c r="D29" t="n">
-        <v>1.15407</v>
+        <v>16.259</v>
+      </c>
+      <c r="E29" t="n">
+        <v>16.2685</v>
+      </c>
+      <c r="F29" t="n">
+        <v>267.98378</v>
       </c>
     </row>
     <row r="30">
@@ -1068,51 +1126,42 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.61551</v>
+        <v>16.04988</v>
       </c>
       <c r="D30" t="n">
-        <v>1.13193</v>
+        <v>16.049</v>
+      </c>
+      <c r="E30" t="n">
+        <v>16.04916</v>
+      </c>
+      <c r="F30" t="n">
+        <v>262.13336</v>
       </c>
     </row>
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Max Stepheight</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Rz mean</t>
+          <t>Min Stepheight</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Rz min</t>
+          <t>Mean Stepheight</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rz max</t>
+          <t>Width</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ra mean</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Ra Std dev</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Ra min</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Ra max</t>
+          <t>Space</t>
         </is>
       </c>
     </row>
@@ -1124,32 +1173,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>roughness</t>
+          <t>Trace 1</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.77501</v>
+        <v>17.18448</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0843</v>
+        <v>16.22658</v>
       </c>
       <c r="E32" t="n">
-        <v>0.61941</v>
+        <v>16.97254</v>
       </c>
       <c r="F32" t="n">
-        <v>0.99348</v>
+        <v>22.21303</v>
       </c>
       <c r="G32" t="n">
-        <v>0.11142</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0.0078</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.09370000000000001</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0.12819</v>
+        <v>34.62561</v>
       </c>
     </row>
     <row r="33">
@@ -1159,28 +1199,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>0.76764</v>
+        <v>17.29168</v>
       </c>
       <c r="D33" t="n">
-        <v>0.08154</v>
+        <v>16.57707</v>
       </c>
       <c r="E33" t="n">
-        <v>0.61641</v>
+        <v>17.02042</v>
       </c>
       <c r="F33" t="n">
-        <v>0.99638</v>
+        <v>22.3986</v>
       </c>
       <c r="G33" t="n">
-        <v>0.11318</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0.00767</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.09549000000000001</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0.13068</v>
+        <v>35.13905</v>
       </c>
     </row>
     <row r="34">
@@ -1190,28 +1221,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>0.7619</v>
+        <v>17.40023</v>
       </c>
       <c r="D34" t="n">
-        <v>0.08180999999999999</v>
+        <v>16.37514</v>
       </c>
       <c r="E34" t="n">
-        <v>0.61827</v>
+        <v>16.76679</v>
       </c>
       <c r="F34" t="n">
-        <v>0.99438</v>
+        <v>22.498</v>
       </c>
       <c r="G34" t="n">
-        <v>0.11008</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0.007820000000000001</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.09735000000000001</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0.13118</v>
+        <v>35.79071</v>
       </c>
     </row>
     <row r="35">
@@ -1221,28 +1243,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.7781</v>
+        <v>17.24777</v>
       </c>
       <c r="D35" t="n">
-        <v>0.08488</v>
+        <v>16.32288</v>
       </c>
       <c r="E35" t="n">
-        <v>0.63971</v>
+        <v>17.02436</v>
       </c>
       <c r="F35" t="n">
-        <v>0.98198</v>
+        <v>22.28161</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1141</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0.00784</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.09512</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0.13075</v>
+        <v>35.70699</v>
       </c>
     </row>
     <row r="36">
@@ -1252,28 +1265,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.77694</v>
+        <v>17.17265</v>
       </c>
       <c r="D36" t="n">
-        <v>0.08222</v>
+        <v>16.69776</v>
       </c>
       <c r="E36" t="n">
-        <v>0.62553</v>
+        <v>16.73825</v>
       </c>
       <c r="F36" t="n">
-        <v>0.99729</v>
+        <v>21.98467</v>
       </c>
       <c r="G36" t="n">
-        <v>0.11439</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0.00776</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.09643</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0.12946</v>
+        <v>35.28669</v>
       </c>
     </row>
     <row r="37">
@@ -1283,28 +1287,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.7806</v>
+        <v>17.22255</v>
       </c>
       <c r="D37" t="n">
-        <v>0.08254</v>
+        <v>16.60829</v>
       </c>
       <c r="E37" t="n">
-        <v>0.61491</v>
+        <v>16.70182</v>
       </c>
       <c r="F37" t="n">
-        <v>0.99308</v>
+        <v>22.58636</v>
       </c>
       <c r="G37" t="n">
-        <v>0.10997</v>
-      </c>
-      <c r="H37" t="n">
-        <v>0.00791</v>
-      </c>
-      <c r="I37" t="n">
-        <v>0.09422999999999999</v>
-      </c>
-      <c r="J37" t="n">
-        <v>0.13107</v>
+        <v>35.26419</v>
       </c>
     </row>
     <row r="38">
@@ -1314,28 +1309,19 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.77032</v>
+        <v>17.22938</v>
       </c>
       <c r="D38" t="n">
-        <v>0.08247</v>
+        <v>16.47326</v>
       </c>
       <c r="E38" t="n">
-        <v>0.63248</v>
+        <v>17.10166</v>
       </c>
       <c r="F38" t="n">
-        <v>0.98916</v>
+        <v>22.55518</v>
       </c>
       <c r="G38" t="n">
-        <v>0.11184</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0.00783</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0.0959</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0.13149</v>
+        <v>35.46807</v>
       </c>
     </row>
     <row r="39">
@@ -1345,28 +1331,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.76913</v>
+        <v>16.98142</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08376</v>
+        <v>16.34166</v>
       </c>
       <c r="E39" t="n">
-        <v>0.62647</v>
+        <v>16.77978</v>
       </c>
       <c r="F39" t="n">
-        <v>1.00676</v>
+        <v>22.24074</v>
       </c>
       <c r="G39" t="n">
-        <v>0.11376</v>
-      </c>
-      <c r="H39" t="n">
-        <v>0.007979999999999999</v>
-      </c>
-      <c r="I39" t="n">
-        <v>0.09687</v>
-      </c>
-      <c r="J39" t="n">
-        <v>0.1326</v>
+        <v>35.2061</v>
       </c>
     </row>
     <row r="40">
@@ -1376,28 +1353,843 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.77227</v>
+        <v>17.06558</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0837</v>
+        <v>16.56186</v>
       </c>
       <c r="E40" t="n">
-        <v>0.62937</v>
+        <v>16.72655</v>
       </c>
       <c r="F40" t="n">
-        <v>0.98863</v>
+        <v>21.87646</v>
       </c>
       <c r="G40" t="n">
-        <v>0.11251</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.00795</v>
-      </c>
-      <c r="I40" t="n">
-        <v>0.09639</v>
-      </c>
-      <c r="J40" t="n">
-        <v>0.12954</v>
+        <v>34.90834</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Max Stepheight</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Min Stepheight</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Mean Stepheight</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Width</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Space</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Trace 2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>16.98739</v>
+      </c>
+      <c r="D42" t="n">
+        <v>16.41647</v>
+      </c>
+      <c r="E42" t="n">
+        <v>16.90877</v>
+      </c>
+      <c r="F42" t="n">
+        <v>22.47528</v>
+      </c>
+      <c r="G42" t="n">
+        <v>36.2659</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>17.71593</v>
+      </c>
+      <c r="D43" t="n">
+        <v>16.59471</v>
+      </c>
+      <c r="E43" t="n">
+        <v>16.74992</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22.18901</v>
+      </c>
+      <c r="G43" t="n">
+        <v>35.50834</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>17.29237</v>
+      </c>
+      <c r="D44" t="n">
+        <v>16.44876</v>
+      </c>
+      <c r="E44" t="n">
+        <v>17.19085</v>
+      </c>
+      <c r="F44" t="n">
+        <v>23.07863</v>
+      </c>
+      <c r="G44" t="n">
+        <v>35.30862</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>17.00627</v>
+      </c>
+      <c r="D45" t="n">
+        <v>16.56766</v>
+      </c>
+      <c r="E45" t="n">
+        <v>16.76465</v>
+      </c>
+      <c r="F45" t="n">
+        <v>22.32655</v>
+      </c>
+      <c r="G45" t="n">
+        <v>35.11242</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>17.42746</v>
+      </c>
+      <c r="D46" t="n">
+        <v>16.13777</v>
+      </c>
+      <c r="E46" t="n">
+        <v>16.9265</v>
+      </c>
+      <c r="F46" t="n">
+        <v>22.35351</v>
+      </c>
+      <c r="G46" t="n">
+        <v>35.12915</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>17.07838</v>
+      </c>
+      <c r="D47" t="n">
+        <v>16.53247</v>
+      </c>
+      <c r="E47" t="n">
+        <v>16.60759</v>
+      </c>
+      <c r="F47" t="n">
+        <v>22.69747</v>
+      </c>
+      <c r="G47" t="n">
+        <v>35.499</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>17.1994</v>
+      </c>
+      <c r="D48" t="n">
+        <v>16.34418</v>
+      </c>
+      <c r="E48" t="n">
+        <v>17.0203</v>
+      </c>
+      <c r="F48" t="n">
+        <v>22.54066</v>
+      </c>
+      <c r="G48" t="n">
+        <v>35.5957</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>17.14933</v>
+      </c>
+      <c r="D49" t="n">
+        <v>16.44957</v>
+      </c>
+      <c r="E49" t="n">
+        <v>16.63013</v>
+      </c>
+      <c r="F49" t="n">
+        <v>22.79847</v>
+      </c>
+      <c r="G49" t="n">
+        <v>34.67306</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>17.04113</v>
+      </c>
+      <c r="D50" t="n">
+        <v>16.63514</v>
+      </c>
+      <c r="E50" t="n">
+        <v>16.96974</v>
+      </c>
+      <c r="F50" t="n">
+        <v>22.4307</v>
+      </c>
+      <c r="G50" t="n">
+        <v>35.00486</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>via 1</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>0.61548</v>
+      </c>
+      <c r="D52" t="n">
+        <v>1.16091</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0.62882</v>
+      </c>
+      <c r="D53" t="n">
+        <v>1.14329</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0.62686</v>
+      </c>
+      <c r="D54" t="n">
+        <v>1.13226</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>0.62971</v>
+      </c>
+      <c r="D55" t="n">
+        <v>1.13498</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>0.6277199999999999</v>
+      </c>
+      <c r="D56" t="n">
+        <v>1.13973</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>0.6141799999999999</v>
+      </c>
+      <c r="D57" t="n">
+        <v>1.14231</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>0.61851</v>
+      </c>
+      <c r="D58" t="n">
+        <v>1.12404</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>0.62526</v>
+      </c>
+      <c r="D59" t="n">
+        <v>1.14413</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>0.61264</v>
+      </c>
+      <c r="D60" t="n">
+        <v>1.14488</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Dimple</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Bump</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>via 2</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>0.62966</v>
+      </c>
+      <c r="D62" t="n">
+        <v>1.11008</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>0.62502</v>
+      </c>
+      <c r="D63" t="n">
+        <v>1.16647</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>0.62065</v>
+      </c>
+      <c r="D64" t="n">
+        <v>1.16022</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>0.63512</v>
+      </c>
+      <c r="D65" t="n">
+        <v>1.14084</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>0.6264</v>
+      </c>
+      <c r="D66" t="n">
+        <v>1.16472</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>0.6201100000000001</v>
+      </c>
+      <c r="D67" t="n">
+        <v>1.14113</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>0.63602</v>
+      </c>
+      <c r="D68" t="n">
+        <v>1.14584</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>0.61512</v>
+      </c>
+      <c r="D69" t="n">
+        <v>1.13652</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>0.60888</v>
+      </c>
+      <c r="D70" t="n">
+        <v>1.14158</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Rz mean</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Rz min</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Rz max</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Ra mean</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Ra Std dev</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Ra min</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Ra max</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Unit 7</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>roughness</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>0.77029</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0.08562</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.6186199999999999</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.98549</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.11093</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.007849999999999999</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.09637999999999999</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.12974</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Unit 8</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>0.7741400000000001</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0.08373999999999999</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.6261100000000001</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.11259</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.00768</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.09554</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.12971</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Unit 9</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>0.77316</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.08382000000000001</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6190099999999999</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.9907899999999999</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.11362</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.00759</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.09547</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.13265</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Unit 4</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>0.77335</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.08538999999999999</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.61609</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.99624</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.11131</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.00774</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.09762999999999999</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.12955</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Unit 5</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>0.77423</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.08315</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.62234</v>
+      </c>
+      <c r="F76" t="n">
+        <v>1.01435</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.11191</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.00781</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.09461</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.13014</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Unit 6</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>0.77238</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.08278000000000001</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.62729</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.99991</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.11156</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.007860000000000001</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.09557</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.12912</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Unit 1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>0.77838</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.08372</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.9687</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.11495</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.00783</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.09656000000000001</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.12811</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Unit 2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>0.76934</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.0824</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.6233300000000001</v>
+      </c>
+      <c r="F79" t="n">
+        <v>1.01327</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.11361</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.09425</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.13013</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Unit 3</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>0.78492</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.08583</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.6130100000000001</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.98421</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.1123</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.09603</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.13243</v>
       </c>
     </row>
   </sheetData>
